--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484651_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484651_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.7472</v>
+        <v>7.3548</v>
       </c>
       <c r="E2" t="n">
-        <v>5.5333</v>
+        <v>5.9179</v>
       </c>
       <c r="F2" t="n">
-        <v>1.2139</v>
+        <v>1.4369</v>
       </c>
       <c r="G2" t="n">
         <v>0.9182</v>
@@ -610,13 +610,13 @@
         <v>3.8484</v>
       </c>
       <c r="S2" t="n">
-        <v>-2.1606</v>
+        <v>-1.553</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.3212</v>
+        <v>-0.9366</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.8393</v>
+        <v>-0.6163</v>
       </c>
       <c r="V2" t="n">
         <v>5.0575</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.0736</v>
+        <v>2.7952</v>
       </c>
       <c r="E3" t="n">
-        <v>2.4244</v>
+        <v>2.6167</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6492</v>
+        <v>0.1785</v>
       </c>
       <c r="G3" t="n">
         <v>2.7623</v>
@@ -688,13 +688,13 @@
         <v>2.1991</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.66</v>
+        <v>-0.9384</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.9909</v>
+        <v>-0.7986</v>
       </c>
       <c r="U3" t="n">
-        <v>0.331</v>
+        <v>-0.1397</v>
       </c>
       <c r="V3" t="n">
         <v>-0.3115</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.9618</v>
+        <v>2.3216</v>
       </c>
       <c r="E4" t="n">
-        <v>2.1744</v>
+        <v>2.559</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.2126</v>
+        <v>-0.2374</v>
       </c>
       <c r="G4" t="n">
         <v>1.0884</v>
@@ -766,13 +766,13 @@
         <v>0.733</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.4931</v>
+        <v>-0.1333</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.4955</v>
+        <v>-0.1108</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0023</v>
+        <v>-0.0224</v>
       </c>
       <c r="V4" t="n">
         <v>0.6335</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.6228</v>
+        <v>1.6199</v>
       </c>
       <c r="E5" t="n">
-        <v>0.4216</v>
+        <v>0.5178</v>
       </c>
       <c r="F5" t="n">
-        <v>1.2012</v>
+        <v>1.1021</v>
       </c>
       <c r="G5" t="n">
         <v>0.259</v>
@@ -844,13 +844,13 @@
         <v>1.8326</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.4688</v>
+        <v>-0.4717</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.4404</v>
+        <v>-0.3443</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.0284</v>
+        <v>-0.1275</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. GONZALEZ SOLER</t>
+          <t>P. BUSTAMANTE CONTRERAS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9169</v>
+        <v>1.5648</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.5351</v>
+        <v>3.2904</v>
       </c>
       <c r="F6" t="n">
-        <v>2.452</v>
+        <v>-1.7256</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.8888</v>
+        <v>0.8612</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.36</v>
+        <v>-0.5815</v>
       </c>
       <c r="I6" t="n">
-        <v>0.4711</v>
+        <v>1.4427</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.3819</v>
+        <v>3.7143</v>
       </c>
       <c r="K6" t="n">
-        <v>-1.1737</v>
+        <v>2.3034</v>
       </c>
       <c r="L6" t="n">
-        <v>0.7917999999999999</v>
+        <v>1.4109</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.5069</v>
+        <v>-2.8531</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.1863</v>
+        <v>-2.8849</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.3207</v>
+        <v>0.0318</v>
       </c>
       <c r="P6" t="n">
-        <v>0.9163</v>
+        <v>-1.8326</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.9163</v>
+        <v>-3.6651</v>
       </c>
       <c r="R6" t="n">
         <v>1.8326</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.3775</v>
+        <v>-1.2647</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.8808</v>
+        <v>-0.8816000000000001</v>
       </c>
       <c r="U6" t="n">
-        <v>0.5033</v>
+        <v>-0.3831</v>
       </c>
       <c r="V6" t="n">
-        <v>1.267</v>
+        <v>3.8009</v>
       </c>
       <c r="W6" t="n">
-        <v>0.6439</v>
+        <v>4.1229</v>
       </c>
       <c r="X6" t="n">
-        <v>0.6231</v>
+        <v>-0.3219</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>P. BUSTAMANTE CONTRERAS</t>
+          <t>A. GONZALEZ SOLER</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.8279</v>
+        <v>0.969</v>
       </c>
       <c r="E7" t="n">
-        <v>2.8507</v>
+        <v>-1.3839</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.0229</v>
+        <v>2.3529</v>
       </c>
       <c r="G7" t="n">
-        <v>0.8612</v>
+        <v>-0.8888</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.5815</v>
+        <v>-1.36</v>
       </c>
       <c r="I7" t="n">
-        <v>1.4427</v>
+        <v>0.4711</v>
       </c>
       <c r="J7" t="n">
-        <v>3.7143</v>
+        <v>-0.3819</v>
       </c>
       <c r="K7" t="n">
-        <v>2.3034</v>
+        <v>-1.1737</v>
       </c>
       <c r="L7" t="n">
-        <v>1.4109</v>
+        <v>0.7917999999999999</v>
       </c>
       <c r="M7" t="n">
-        <v>-2.8531</v>
+        <v>-0.5069</v>
       </c>
       <c r="N7" t="n">
-        <v>-2.8849</v>
+        <v>-0.1863</v>
       </c>
       <c r="O7" t="n">
-        <v>0.0318</v>
+        <v>-0.3207</v>
       </c>
       <c r="P7" t="n">
-        <v>-1.8326</v>
+        <v>0.9163</v>
       </c>
       <c r="Q7" t="n">
-        <v>-3.6651</v>
+        <v>-0.9163</v>
       </c>
       <c r="R7" t="n">
         <v>1.8326</v>
       </c>
       <c r="S7" t="n">
-        <v>-2.0016</v>
+        <v>-0.3254</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.3212</v>
+        <v>-0.7296</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.6804</v>
+        <v>0.4042</v>
       </c>
       <c r="V7" t="n">
-        <v>3.8009</v>
+        <v>1.267</v>
       </c>
       <c r="W7" t="n">
-        <v>4.1229</v>
+        <v>0.6439</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.3219</v>
+        <v>0.6231</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.8255</v>
+        <v>0.3095</v>
       </c>
       <c r="E8" t="n">
-        <v>0.9907</v>
+        <v>0.2765</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.1652</v>
+        <v>0.033</v>
       </c>
       <c r="G8" t="n">
         <v>-1.696</v>
@@ -1078,13 +1078,13 @@
         <v>4.0317</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.5835</v>
+        <v>-1.0995</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.2594</v>
+        <v>-0.9736</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.3242</v>
+        <v>-0.126</v>
       </c>
       <c r="V8" t="n">
         <v>-0.0104</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.4423</v>
+        <v>-0.703</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.823</v>
+        <v>-1.2076</v>
       </c>
       <c r="F9" t="n">
-        <v>0.3807</v>
+        <v>0.5046</v>
       </c>
       <c r="G9" t="n">
         <v>-0.6627999999999999</v>
@@ -1156,13 +1156,13 @@
         <v>2.5656</v>
       </c>
       <c r="S9" t="n">
-        <v>0.0818</v>
+        <v>-0.1789</v>
       </c>
       <c r="T9" t="n">
-        <v>0.3462</v>
+        <v>-0.0384</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2643</v>
+        <v>-0.1405</v>
       </c>
       <c r="V9" t="n">
         <v>0.3219</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>S. DOMINGUEZ ALEIXANDRE</t>
+          <t>M. CORNEJO GONZALEZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.9298999999999999</v>
+        <v>-0.8954</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.4742</v>
+        <v>-1.5113</v>
       </c>
       <c r="F10" t="n">
-        <v>0.5443</v>
+        <v>0.6159</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.8759</v>
+        <v>-0.98</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.065</v>
+        <v>-1.7718</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.8109</v>
+        <v>0.7917999999999999</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.3293</v>
+        <v>-0.392</v>
       </c>
       <c r="K10" t="n">
-        <v>0.1609</v>
+        <v>-1.793</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.4902</v>
+        <v>1.401</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.5466</v>
+        <v>-0.5879</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.2259</v>
+        <v>0.0213</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.3207</v>
+        <v>-0.6092</v>
       </c>
       <c r="P10" t="n">
-        <v>1.0995</v>
+        <v>2.3823</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.9163</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>2.0158</v>
+        <v>2.3823</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.2085</v>
+        <v>-0.7193000000000001</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.5505</v>
+        <v>-0.4962</v>
       </c>
       <c r="U10" t="n">
-        <v>0.3421</v>
+        <v>-0.2231</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.945</v>
+        <v>-1.5785</v>
       </c>
       <c r="W10" t="n">
-        <v>0.3219</v>
+        <v>-0.6231</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.267</v>
+        <v>-0.9554</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>M. CORNEJO GONZALEZ</t>
+          <t>S. DOMINGUEZ ALEIXANDRE</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.4094</v>
+        <v>-0.9273</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.951</v>
+        <v>-1.323</v>
       </c>
       <c r="F11" t="n">
-        <v>0.5416</v>
+        <v>0.3957</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.98</v>
+        <v>-0.8759</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.7718</v>
+        <v>-0.065</v>
       </c>
       <c r="I11" t="n">
-        <v>0.7917999999999999</v>
+        <v>-0.8109</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.392</v>
+        <v>-0.3293</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.793</v>
+        <v>0.1609</v>
       </c>
       <c r="L11" t="n">
-        <v>1.401</v>
+        <v>-0.4902</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.5879</v>
+        <v>-0.5466</v>
       </c>
       <c r="N11" t="n">
-        <v>0.0213</v>
+        <v>-0.2259</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.6092</v>
+        <v>-0.3207</v>
       </c>
       <c r="P11" t="n">
-        <v>2.3823</v>
+        <v>1.0995</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>-0.9163</v>
       </c>
       <c r="R11" t="n">
-        <v>2.3823</v>
+        <v>2.0158</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.2333</v>
+        <v>-0.2059</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.9359</v>
+        <v>-0.3993</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.2974</v>
+        <v>0.1934</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.5785</v>
+        <v>-0.945</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.6231</v>
+        <v>0.3219</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.9554</v>
+        <v>-1.267</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.8343</v>
+        <v>-5.7741</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.3535</v>
+        <v>-3.2189</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.4808</v>
+        <v>-2.5551</v>
       </c>
       <c r="G12" t="n">
         <v>-3.0744</v>
@@ -1390,13 +1390,13 @@
         <v>1.4661</v>
       </c>
       <c r="S12" t="n">
-        <v>1.1405</v>
+        <v>0.2008</v>
       </c>
       <c r="T12" t="n">
-        <v>1.1524</v>
+        <v>0.287</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.0119</v>
+        <v>-0.0862</v>
       </c>
       <c r="V12" t="n">
         <v>-2.5339</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>8.3598</v>
+        <v>8.634999999999998</v>
       </c>
       <c r="E13" t="n">
-        <v>6.258299999999998</v>
+        <v>6.533600000000002</v>
       </c>
       <c r="F13" t="n">
-        <v>2.1014</v>
+        <v>2.1015</v>
       </c>
       <c r="G13" t="n">
         <v>-2.288799999999999</v>
@@ -1438,7 +1438,7 @@
         <v>-1.9691</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.32</v>
+        <v>-0.3200000000000001</v>
       </c>
       <c r="J13" t="n">
         <v>12.0619</v>
@@ -1468,10 +1468,10 @@
         <v>24.7398</v>
       </c>
       <c r="S13" t="n">
-        <v>-6.9646</v>
+        <v>-6.6893</v>
       </c>
       <c r="T13" t="n">
-        <v>-5.6972</v>
+        <v>-5.422</v>
       </c>
       <c r="U13" t="n">
         <v>-1.2672</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>M. LARA BARRACHINA</t>
+          <t>H. GARCIA GIRALDA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.5873</v>
+        <v>2.9171</v>
       </c>
       <c r="E14" t="n">
-        <v>1.9681</v>
+        <v>1.9551</v>
       </c>
       <c r="F14" t="n">
-        <v>1.6192</v>
+        <v>0.9619</v>
       </c>
       <c r="G14" t="n">
-        <v>4.1074</v>
+        <v>1.837</v>
       </c>
       <c r="H14" t="n">
-        <v>4.2136</v>
+        <v>-0.2979</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.1062</v>
+        <v>2.1349</v>
       </c>
       <c r="J14" t="n">
-        <v>6.5105</v>
+        <v>1.8311</v>
       </c>
       <c r="K14" t="n">
-        <v>5.7187</v>
+        <v>-0.1116</v>
       </c>
       <c r="L14" t="n">
-        <v>0.7917999999999999</v>
+        <v>1.9428</v>
       </c>
       <c r="M14" t="n">
-        <v>-2.4032</v>
+        <v>0.0059</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.5051</v>
+        <v>-0.1863</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.898</v>
+        <v>0.1922</v>
       </c>
       <c r="P14" t="n">
-        <v>-3.8484</v>
+        <v>1.2828</v>
       </c>
       <c r="Q14" t="n">
-        <v>-5.8642</v>
+        <v>-0.3665</v>
       </c>
       <c r="R14" t="n">
-        <v>2.0158</v>
+        <v>1.6493</v>
       </c>
       <c r="S14" t="n">
-        <v>2.674</v>
+        <v>0.7423</v>
       </c>
       <c r="T14" t="n">
-        <v>0.034</v>
+        <v>0.1686</v>
       </c>
       <c r="U14" t="n">
-        <v>2.6401</v>
+        <v>0.5737</v>
       </c>
       <c r="V14" t="n">
-        <v>0.6543</v>
+        <v>-0.945</v>
       </c>
       <c r="W14" t="n">
-        <v>1.2878</v>
+        <v>0.3219</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.6335</v>
+        <v>-1.267</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>H. GARCIA GIRALDA</t>
+          <t>M. LARA BARRACHINA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.3672</v>
+        <v>2.7421</v>
       </c>
       <c r="E15" t="n">
-        <v>2.6282</v>
+        <v>2.0642</v>
       </c>
       <c r="F15" t="n">
-        <v>0.739</v>
+        <v>0.6778</v>
       </c>
       <c r="G15" t="n">
-        <v>1.837</v>
+        <v>4.1074</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.2979</v>
+        <v>4.2136</v>
       </c>
       <c r="I15" t="n">
-        <v>2.1349</v>
+        <v>-0.1062</v>
       </c>
       <c r="J15" t="n">
-        <v>1.8311</v>
+        <v>6.5105</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.1116</v>
+        <v>5.7187</v>
       </c>
       <c r="L15" t="n">
-        <v>1.9428</v>
+        <v>0.7917999999999999</v>
       </c>
       <c r="M15" t="n">
-        <v>0.0059</v>
+        <v>-2.4032</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.1863</v>
+        <v>-1.5051</v>
       </c>
       <c r="O15" t="n">
-        <v>0.1922</v>
+        <v>-0.898</v>
       </c>
       <c r="P15" t="n">
-        <v>1.2828</v>
+        <v>-3.8484</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.3665</v>
+        <v>-5.8642</v>
       </c>
       <c r="R15" t="n">
-        <v>1.6493</v>
+        <v>2.0158</v>
       </c>
       <c r="S15" t="n">
-        <v>1.1924</v>
+        <v>1.8288</v>
       </c>
       <c r="T15" t="n">
-        <v>0.8416</v>
+        <v>0.1301</v>
       </c>
       <c r="U15" t="n">
-        <v>0.3507</v>
+        <v>1.6987</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.945</v>
+        <v>0.6543</v>
       </c>
       <c r="W15" t="n">
-        <v>0.3219</v>
+        <v>1.2878</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.267</v>
+        <v>-0.6335</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.2189</v>
+        <v>1.3965</v>
       </c>
       <c r="E16" t="n">
-        <v>-2.4978</v>
+        <v>-1.8247</v>
       </c>
       <c r="F16" t="n">
-        <v>3.7167</v>
+        <v>3.2213</v>
       </c>
       <c r="G16" t="n">
         <v>1.3589</v>
@@ -1702,13 +1702,13 @@
         <v>2.5656</v>
       </c>
       <c r="S16" t="n">
-        <v>1.3944</v>
+        <v>1.572</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.3137</v>
+        <v>0.3594</v>
       </c>
       <c r="U16" t="n">
-        <v>1.7081</v>
+        <v>1.2126</v>
       </c>
       <c r="V16" t="n">
         <v>3.7801</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.4303</v>
+        <v>-0.4056</v>
       </c>
       <c r="E19" t="n">
         <v>-0.0134</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.417</v>
+        <v>-0.3922</v>
       </c>
       <c r="G19" t="n">
         <v>-0.2636</v>
@@ -1936,13 +1936,13 @@
         <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.1667</v>
+        <v>-0.142</v>
       </c>
       <c r="T19" t="n">
         <v>-0.0551</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.1117</v>
+        <v>-0.08690000000000001</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>B. KABASELE KATUMBA</t>
+          <t>J. BALFAGON MIRAVET</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.7167</v>
+        <v>-0.6367</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.3975</v>
+        <v>1.4651</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.3193</v>
+        <v>-2.1018</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.7046</v>
+        <v>0.1788</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.5312</v>
+        <v>1.8137</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.1734</v>
+        <v>-1.6348</v>
       </c>
       <c r="J20" t="n">
-        <v>0.3001</v>
+        <v>2.6217</v>
       </c>
       <c r="K20" t="n">
-        <v>0.2167</v>
+        <v>3.1021</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0833</v>
+        <v>-0.4804</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.0047</v>
+        <v>-2.4428</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.748</v>
+        <v>-1.2884</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.2567</v>
+        <v>-1.1544</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.1833</v>
+        <v>-1.2828</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.9163</v>
+        <v>-3.2986</v>
       </c>
       <c r="R20" t="n">
-        <v>0.733</v>
+        <v>2.0158</v>
       </c>
       <c r="S20" t="n">
-        <v>0.8046</v>
+        <v>1.0903</v>
       </c>
       <c r="T20" t="n">
-        <v>0.2187</v>
+        <v>0.2312</v>
       </c>
       <c r="U20" t="n">
-        <v>0.5859</v>
+        <v>0.8591</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.6335</v>
+        <v>-0.6231</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.9109</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.6335</v>
+        <v>-2.5339</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>M. BALFAGON SULLER</t>
+          <t>B. KABASELE KATUMBA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.4927</v>
+        <v>-0.9804</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.2786</v>
+        <v>-0.6859</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.2141</v>
+        <v>-0.2945</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.472</v>
+        <v>-0.7046</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.9433</v>
+        <v>-0.5312</v>
       </c>
       <c r="I21" t="n">
-        <v>1.4713</v>
+        <v>-0.1734</v>
       </c>
       <c r="J21" t="n">
-        <v>0.1799</v>
+        <v>0.3001</v>
       </c>
       <c r="K21" t="n">
-        <v>-1.1954</v>
+        <v>0.2167</v>
       </c>
       <c r="L21" t="n">
-        <v>1.3753</v>
+        <v>0.0833</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.6519</v>
+        <v>-1.0047</v>
       </c>
       <c r="N21" t="n">
         <v>-0.748</v>
       </c>
       <c r="O21" t="n">
-        <v>0.0961</v>
+        <v>-0.2567</v>
       </c>
       <c r="P21" t="n">
-        <v>0.3665</v>
+        <v>-0.1833</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.1833</v>
+        <v>-0.9163</v>
       </c>
       <c r="R21" t="n">
-        <v>0.5498</v>
+        <v>0.733</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.4318</v>
+        <v>0.5409</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.2753</v>
+        <v>-0.0697</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.1566</v>
+        <v>0.6107</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.9554</v>
+        <v>-0.6335</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.9554</v>
+        <v>-0.6335</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>J. TORRES HERNANDO</t>
+          <t>M. BALFAGON SULLER</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,40 +2125,40 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.6238</v>
+        <v>-1.3034</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.7027</v>
+        <v>0.0098</v>
       </c>
       <c r="F22" t="n">
-        <v>0.0789</v>
+        <v>-1.3132</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.1948</v>
+        <v>-0.472</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.2751</v>
+        <v>-1.9433</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.9197</v>
+        <v>1.4713</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.8482</v>
+        <v>0.1799</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.576</v>
+        <v>-1.1954</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.2722</v>
+        <v>1.3753</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.3466</v>
+        <v>-0.6519</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.6991000000000001</v>
+        <v>-0.748</v>
       </c>
       <c r="O22" t="n">
-        <v>0.3525</v>
+        <v>0.0961</v>
       </c>
       <c r="P22" t="n">
         <v>0.3665</v>
@@ -2170,28 +2170,28 @@
         <v>0.5498</v>
       </c>
       <c r="S22" t="n">
-        <v>0.2045</v>
+        <v>-0.2425</v>
       </c>
       <c r="T22" t="n">
-        <v>0.3288</v>
+        <v>0.0132</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1243</v>
+        <v>-0.2557</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>-0.9554</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>-0.9554</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>J. BALFAGON MIRAVET</t>
+          <t>J. TORRES HERNANDO</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.6814</v>
+        <v>-1.6179</v>
       </c>
       <c r="E23" t="n">
-        <v>0.792</v>
+        <v>-1.895</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.4734</v>
+        <v>0.2771</v>
       </c>
       <c r="G23" t="n">
-        <v>0.1788</v>
+        <v>-2.1948</v>
       </c>
       <c r="H23" t="n">
-        <v>1.8137</v>
+        <v>-1.2751</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.6348</v>
+        <v>-0.9197</v>
       </c>
       <c r="J23" t="n">
-        <v>2.6217</v>
+        <v>-1.8482</v>
       </c>
       <c r="K23" t="n">
-        <v>3.1021</v>
+        <v>-0.576</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.4804</v>
+        <v>-1.2722</v>
       </c>
       <c r="M23" t="n">
-        <v>-2.4428</v>
+        <v>-0.3466</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.2884</v>
+        <v>-0.6991000000000001</v>
       </c>
       <c r="O23" t="n">
-        <v>-1.1544</v>
+        <v>0.3525</v>
       </c>
       <c r="P23" t="n">
-        <v>-1.2828</v>
+        <v>0.3665</v>
       </c>
       <c r="Q23" t="n">
-        <v>-3.2986</v>
+        <v>-0.1833</v>
       </c>
       <c r="R23" t="n">
-        <v>2.0158</v>
+        <v>0.5498</v>
       </c>
       <c r="S23" t="n">
-        <v>0.0456</v>
+        <v>0.2104</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.4419</v>
+        <v>0.1365</v>
       </c>
       <c r="U23" t="n">
-        <v>0.4875</v>
+        <v>0.07389999999999999</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.6231</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>1.9109</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-2.5339</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.0966</v>
+        <v>-2.728</v>
       </c>
       <c r="E24" t="n">
-        <v>0.7811</v>
+        <v>0.8772</v>
       </c>
       <c r="F24" t="n">
-        <v>-3.8777</v>
+        <v>-3.6052</v>
       </c>
       <c r="G24" t="n">
         <v>0.5476</v>
@@ -2326,13 +2326,13 @@
         <v>1.0995</v>
       </c>
       <c r="S24" t="n">
-        <v>0.2171</v>
+        <v>0.5858</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.1666</v>
+        <v>-0.07049999999999999</v>
       </c>
       <c r="U24" t="n">
-        <v>0.3838</v>
+        <v>0.6563</v>
       </c>
       <c r="V24" t="n">
         <v>-2.212</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-3.25</v>
+        <v>-2.7604</v>
       </c>
       <c r="E25" t="n">
-        <v>-1.3467</v>
+        <v>-1.1544</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.9033</v>
+        <v>-1.6061</v>
       </c>
       <c r="G25" t="n">
         <v>-1.2983</v>
@@ -2404,13 +2404,13 @@
         <v>0.733</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.4074</v>
+        <v>0.0822</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.4774</v>
+        <v>-0.2851</v>
       </c>
       <c r="U25" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.3673</v>
       </c>
       <c r="V25" t="n">
         <v>-1.9109</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-4.3715</v>
+        <v>-5.1131</v>
       </c>
       <c r="E26" t="n">
-        <v>-2.381</v>
+        <v>-3.2464</v>
       </c>
       <c r="F26" t="n">
-        <v>-1.9905</v>
+        <v>-1.8667</v>
       </c>
       <c r="G26" t="n">
         <v>-0.9376</v>
@@ -2482,13 +2482,13 @@
         <v>0.9163</v>
       </c>
       <c r="S26" t="n">
-        <v>1.4378</v>
+        <v>0.6963</v>
       </c>
       <c r="T26" t="n">
-        <v>1.5739</v>
+        <v>0.7085</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.1361</v>
+        <v>-0.0123</v>
       </c>
       <c r="V26" t="n">
         <v>-2.8559</v>
@@ -2515,16 +2515,16 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-8.3596</v>
+        <v>-8.3598</v>
       </c>
       <c r="E27" t="n">
-        <v>-2.1015</v>
+        <v>-2.1016</v>
       </c>
       <c r="F27" t="n">
-        <v>-6.2582</v>
+        <v>-6.2583</v>
       </c>
       <c r="G27" t="n">
-        <v>2.2888</v>
+        <v>2.288800000000001</v>
       </c>
       <c r="H27" t="n">
         <v>1.969200000000001</v>
@@ -2539,7 +2539,7 @@
         <v>11.4637</v>
       </c>
       <c r="L27" t="n">
-        <v>2.8869</v>
+        <v>2.886899999999999</v>
       </c>
       <c r="M27" t="n">
         <v>-12.0619</v>
@@ -2563,10 +2563,10 @@
         <v>6.964500000000001</v>
       </c>
       <c r="T27" t="n">
-        <v>1.267</v>
+        <v>1.2671</v>
       </c>
       <c r="U27" t="n">
-        <v>5.6974</v>
+        <v>5.697400000000001</v>
       </c>
       <c r="V27" t="n">
         <v>-5.7014</v>
